--- a/output/pdf_financials_xlsx/KS.xlsx
+++ b/output/pdf_financials_xlsx/KS.xlsx
@@ -5596,43 +5596,43 @@
         <v>2.495962</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.495962</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.74551</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.82011</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.87986</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.95201</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.337036</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.832578</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.847828</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.883853</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.063373</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.009643</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>5.009643</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>5.396304</v>
       </c>
     </row>
     <row r="93">
@@ -10272,7 +10272,11 @@
           <t>Reserves (Note 15)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -12038,7 +12042,11 @@
           <t>Reserves (Note 13)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -12686,7 +12694,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -17082,7 +17094,11 @@
           <t>Share-based Payments Reserve</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KS.xlsx
+++ b/output/pdf_financials_xlsx/KS.xlsx
@@ -2327,25 +2327,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.181474</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.131637</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.043339</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.014047</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.020301</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.432679</v>
@@ -2360,19 +2360,19 @@
         <v>0.034769</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.002016</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.800959</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.157305</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.000107</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.001426</v>
       </c>
     </row>
     <row r="35">
@@ -2437,25 +2437,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.181474</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.131637</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.19725</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.043339</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.014047</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.020301</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.432679</v>
@@ -2470,19 +2470,19 @@
         <v>0.034769</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.002016</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.800959</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.157305</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.000107</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.001426</v>
       </c>
     </row>
     <row r="37">
@@ -3097,25 +3097,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.283548</v>
+        <v>0.102074</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.008134000000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.13366</v>
+        <v>0.002023</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.005914</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.047754</v>
+        <v>0.004415</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.031118</v>
+        <v>0.017071</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.02573</v>
+        <v>0.005429</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.006202</v>
@@ -3130,19 +3130,19 @@
         <v>0.02022</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.004712</v>
+        <v>0.002696</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.81349</v>
+        <v>0.012531</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.167603</v>
+        <v>0.010298</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.02414</v>
+        <v>0.024033</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.005176</v>
+        <v>0.00375</v>
       </c>
     </row>
     <row r="49">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/KS.xlsx
+++ b/output/pdf_financials_xlsx/KS.xlsx
@@ -1292,7 +1292,7 @@
         <v>2.019577</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.765483</v>
+        <v>-0.016</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -2184,7 +2184,7 @@
         <v>-65.14510240084176</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-40.21819710243915</v>
+        <v>-0.8406341533894631</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -6567,16 +6567,16 @@
         <v>0</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.326757</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.07585699999999999</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.178345</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.167218</v>
       </c>
     </row>
     <row r="111">
@@ -6818,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.181768</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -19176,7 +19176,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -25940,7 +25944,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -26318,7 +26326,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -27452,7 +27464,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -28690,7 +28706,11 @@
           <t>Proceeds from shares issuances</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -31380,7 +31400,11 @@
           <t>Proceeds from shares issuance</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -31952,7 +31976,11 @@
           <t>Future income taxes recovered</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E261" s="5" t="n">
         <v>-1.469</v>
       </c>
@@ -42114,7 +42142,11 @@
           <t>Deferred Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
